--- a/iwpb-sg-dashboard/IWPB_Global_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_Global_config_pack.xlsx
@@ -11793,12 +11793,6 @@
           <t>&lt;One calculation per group of rows. Include: + adds the line, − takes it out, / makes it the denominator of a ratio. MICA level names the column the line lives in. Product Level optionally qualifies it: a bare column name lets the line be found there too, "Product_Level_7 = Insurance Manufacturing" restricts it to those rows. A line taken out is removed from the selection where it sits inside the base, and subtracted where it does not.&gt;</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11826,8 +11820,6 @@
           <t>MICA_Level_3</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11857,10 +11849,9 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Product_Level_7 = Insurance Manufacturing</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Product_Level_4 = Insurance</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11888,8 +11879,6 @@
           <t>accH3</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/iwpb-sg-dashboard/IWPB_Global_config_pack.xlsx
+++ b/iwpb-sg-dashboard/IWPB_Global_config_pack.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1356,121 +1356,145 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b|headcount|\bfte\b|\bcount\b</t>
+          <t>%|\bbps\b|\brote\b|\bcer\b|\bratio\b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>commentary_driver_floor</t>
+          <t>count_patterns</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>headcount|\bfte\b|\bcounts?\b|customers|\bnos\b|\bnumber\b|\bheads\b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>commentary_driver_cover</t>
+          <t>commentary_driver_floor</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>commentary_max_notes</t>
+          <t>commentary_driver_cover</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>fsum_notes</t>
+          <t>commentary_max_notes</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fsum_note_lines</t>
+          <t>fsum_notes</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tile_visible</t>
+          <t>fsum_note_lines</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>tile_net</t>
+          <t>tile_visible</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>tile_net_auto</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>tile_net</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>revenue_patterns</t>
+          <t>tile_net_auto</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>tile_height</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>150</v>
+          <t>revenue_patterns</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>revenue|income|\bfees?\b|\bnii\b|turnover|\bnnii\b</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>tile_height</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>tile_min_width</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B94" t="n">
         <v>252</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tile_unit_label</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
     </row>
   </sheetData>
